--- a/03_Outputs/De_la_Paz/05_Economia/economia.xlsx
+++ b/03_Outputs/De_la_Paz/05_Economia/economia.xlsx
@@ -7327,10 +7327,8 @@
       <c r="F4" s="118">
         <v>25.3843592796398</v>
       </c>
-      <c r="G4" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G4" s="120">
+        <v>0.0679195087900003</v>
       </c>
       <c r="H4" s="122">
         <v>20.89614611041</v>
@@ -7509,7 +7507,7 @@
         <v>186.744639013839</v>
       </c>
       <c r="G7" s="121">
-        <v>95.8201286018905</v>
+        <v>95.8880481106805</v>
       </c>
       <c r="H7" s="123">
         <v>355.74423124851</v>
@@ -7685,10 +7683,8 @@
       <c r="F10" s="118">
         <v>19.2118528469009</v>
       </c>
-      <c r="G10" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G10" s="120">
+        <v>0.0821323914101296</v>
       </c>
       <c r="H10" s="122">
         <v>19.1131444783331</v>
@@ -7867,7 +7863,7 @@
         <v>202.67762206737</v>
       </c>
       <c r="G13" s="121">
-        <v>15.7361286790472</v>
+        <v>15.8182610704573</v>
       </c>
       <c r="H13" s="123">
         <v>349.19422442452</v>
@@ -8399,10 +8395,8 @@
       <c r="F22" s="118">
         <v>22.5678739694862</v>
       </c>
-      <c r="G22" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G22" s="120">
+        <v>0.0203612203640625</v>
       </c>
       <c r="H22" s="122">
         <v>28.5291733909899</v>
@@ -8581,7 +8575,7 @@
         <v>260.136069686487</v>
       </c>
       <c r="G25" s="121">
-        <v>4.60000113965628</v>
+        <v>4.62036236002034</v>
       </c>
       <c r="H25" s="123">
         <v>321.058744689646</v>
@@ -8757,10 +8751,8 @@
       <c r="F28" s="118">
         <v>26.800209699028</v>
       </c>
-      <c r="G28" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G28" s="120">
+        <v>0.0246583130705816</v>
       </c>
       <c r="H28" s="122">
         <v>24.8323465693874</v>
@@ -8939,7 +8931,7 @@
         <v>464.374675843233</v>
       </c>
       <c r="G31" s="121">
-        <v>25.464696615108</v>
+        <v>25.4893549281785</v>
       </c>
       <c r="H31" s="123">
         <v>339.460630698547</v>
@@ -10124,10 +10116,8 @@
       <c r="F51" s="118">
         <v>12.8296639218443</v>
       </c>
-      <c r="G51" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G51" s="120">
+        <v>0.0185878998830093</v>
       </c>
       <c r="H51" s="122">
         <v>2.20453422709976</v>
@@ -10185,10 +10175,8 @@
       <c r="F52" s="118">
         <v>54.5914205949086</v>
       </c>
-      <c r="G52" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G52" s="120">
+        <v>0.0310397104974013</v>
       </c>
       <c r="H52" s="122">
         <v>24.4785696538086</v>
@@ -10367,7 +10355,7 @@
         <v>501.005743878655</v>
       </c>
       <c r="G55" s="121">
-        <v>20.2324369616608</v>
+        <v>20.2820645720412</v>
       </c>
       <c r="H55" s="123">
         <v>308.484767342934</v>
@@ -10425,10 +10413,8 @@
       <c r="F56" s="118">
         <v>122.439728506104</v>
       </c>
-      <c r="G56" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G56" s="120">
+        <v>0.0899446208199414</v>
       </c>
       <c r="H56" s="122">
         <v>9.49564607365835</v>
@@ -10545,10 +10531,8 @@
       <c r="F58" s="118">
         <v>57.8923106270893</v>
       </c>
-      <c r="G58" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G58" s="120">
+        <v>0.086279793377037</v>
       </c>
       <c r="H58" s="122">
         <v>22.8447253604592</v>
@@ -10727,7 +10711,7 @@
         <v>544.254628054419</v>
       </c>
       <c r="G61" s="121">
-        <v>8.68715411067941</v>
+        <v>8.86337852487639</v>
       </c>
       <c r="H61" s="123">
         <v>314.115867928293</v>
@@ -13313,7 +13297,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>8.68715411067941</v>
+        <v>8.86337852487639</v>
       </c>
     </row>
     <row r="4">
